--- a/Datos Tesis Upstream/Computacion Emergente/2526-2/Emergente 2526-2.xlsx
+++ b/Datos Tesis Upstream/Computacion Emergente/2526-2/Emergente 2526-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelsoncarrillo/Downloads/tesis-prediccion-participacion/Datos Tesis Upstream/Computacion Emergente/2526-2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37A00331-3CF4-A14F-A8DB-09D70CD50CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832384D8-88F0-404E-A922-244E56D3DD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="162">
   <si>
     <t>Participaciones Computacion Emergente - Enero-Marzo 2026</t>
   </si>
@@ -670,6 +670,9 @@
   <si>
     <t>jueves</t>
   </si>
+  <si>
+    <t>carnet</t>
+  </si>
 </sst>
 </file>
 
@@ -678,7 +681,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -747,6 +750,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -780,7 +797,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -803,11 +820,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9BC2E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9BC2E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -865,6 +893,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4383,17 +4421,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AD61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="19.83203125" customWidth="1"/>
     <col min="3" max="3" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="28" width="9" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="6" max="29" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -4401,7 +4439,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -4409,7 +4447,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -4417,7 +4455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A5" s="24" t="s">
         <v>61</v>
       </c>
@@ -4430,134 +4468,138 @@
       <c r="D5" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="24"/>
+      <c r="H5" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24" t="s">
+      <c r="I5" s="24"/>
+      <c r="J5" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="24"/>
+      <c r="L5" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24" t="s">
+      <c r="M5" s="24"/>
+      <c r="N5" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24" t="s">
+      <c r="O5" s="24"/>
+      <c r="P5" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24" t="s">
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24" t="s">
+      <c r="S5" s="24"/>
+      <c r="T5" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24" t="s">
+      <c r="U5" s="24"/>
+      <c r="V5" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24" t="s">
+      <c r="W5" s="24"/>
+      <c r="X5" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="24" t="s">
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="Z5" s="24"/>
-      <c r="AA5" s="24" t="s">
+      <c r="AA5" s="24"/>
+      <c r="AB5" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="AB5" s="24"/>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AC5" s="24"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A6" s="24"/>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="25"/>
+      <c r="F6" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="G6" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="H6" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="I6" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="J6" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="K6" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="L6" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="L6" s="16" t="s">
+      <c r="M6" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="M6" s="16" t="s">
+      <c r="N6" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="N6" s="16" t="s">
+      <c r="O6" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="O6" s="16" t="s">
+      <c r="P6" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="P6" s="16" t="s">
+      <c r="Q6" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="Q6" s="16" t="s">
+      <c r="R6" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="R6" s="16" t="s">
+      <c r="S6" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="S6" s="16" t="s">
+      <c r="T6" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="T6" s="16" t="s">
+      <c r="U6" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="U6" s="16" t="s">
+      <c r="V6" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="V6" s="16" t="s">
+      <c r="W6" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="W6" s="16" t="s">
+      <c r="X6" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="X6" s="16" t="s">
+      <c r="Y6" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="Y6" s="16" t="s">
+      <c r="Z6" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="Z6" s="16" t="s">
+      <c r="AA6" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="AA6" s="16" t="s">
+      <c r="AB6" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="AB6" s="16" t="s">
+      <c r="AC6" s="16" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="19">
         <v>1</v>
       </c>
@@ -4570,35 +4612,38 @@
       <c r="D7" s="21">
         <v>31068474</v>
       </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="19">
-        <v>1</v>
-      </c>
-      <c r="I7" s="22"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="22"/>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="22"/>
-      <c r="Z7" s="19"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="19"/>
+      <c r="E7" s="27">
+        <v>20231110073</v>
+      </c>
+      <c r="F7" s="22"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="19">
+        <v>1</v>
+      </c>
+      <c r="J7" s="22"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="19"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="22"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="19"/>
+      <c r="AB7" s="22"/>
       <c r="AC7" s="19"/>
-    </row>
-    <row r="8" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD7" s="19"/>
+    </row>
+    <row r="8" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="19">
         <v>2</v>
       </c>
@@ -4611,33 +4656,36 @@
       <c r="D8" s="21">
         <v>29510447</v>
       </c>
-      <c r="E8" s="22"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="22"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="22"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="19"/>
+      <c r="E8" s="28">
+        <v>20181120049</v>
+      </c>
+      <c r="F8" s="22"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="22"/>
+      <c r="W8" s="19"/>
+      <c r="X8" s="22"/>
+      <c r="Y8" s="19"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="19"/>
+      <c r="AB8" s="22"/>
       <c r="AC8" s="19"/>
-    </row>
-    <row r="9" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD8" s="19"/>
+    </row>
+    <row r="9" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="19">
         <v>3</v>
       </c>
@@ -4650,33 +4698,36 @@
       <c r="D9" s="21">
         <v>25947729</v>
       </c>
-      <c r="E9" s="22"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="19"/>
+      <c r="E9" s="27">
+        <v>20171111081</v>
+      </c>
+      <c r="F9" s="22"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="22"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="19"/>
+      <c r="AB9" s="22"/>
       <c r="AC9" s="19"/>
-    </row>
-    <row r="10" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD9" s="19"/>
+    </row>
+    <row r="10" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="19">
         <v>4</v>
       </c>
@@ -4689,45 +4740,48 @@
       <c r="D10" s="21">
         <v>27849723</v>
       </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="19">
-        <v>1</v>
-      </c>
-      <c r="K10" s="22">
-        <v>1</v>
-      </c>
-      <c r="L10" s="19">
-        <v>1</v>
-      </c>
-      <c r="M10" s="22"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="19">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="22">
-        <v>1</v>
-      </c>
-      <c r="T10" s="19"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="19">
-        <v>1</v>
-      </c>
-      <c r="W10" s="22"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="19"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="19"/>
+      <c r="E10" s="27">
+        <v>20221110382</v>
+      </c>
+      <c r="F10" s="22"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="19">
+        <v>1</v>
+      </c>
+      <c r="L10" s="22">
+        <v>1</v>
+      </c>
+      <c r="M10" s="19">
+        <v>1</v>
+      </c>
+      <c r="N10" s="22"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="19">
+        <v>1</v>
+      </c>
+      <c r="R10" s="22"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="22">
+        <v>1</v>
+      </c>
+      <c r="U10" s="19"/>
+      <c r="V10" s="22"/>
+      <c r="W10" s="19">
+        <v>1</v>
+      </c>
+      <c r="X10" s="22"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="19"/>
+      <c r="AB10" s="22"/>
       <c r="AC10" s="19"/>
-    </row>
-    <row r="11" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD10" s="19"/>
+    </row>
+    <row r="11" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="19">
         <v>5</v>
       </c>
@@ -4740,33 +4794,36 @@
       <c r="D11" s="21">
         <v>30057442</v>
       </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="19"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="19"/>
+      <c r="E11" s="27">
+        <v>20221110439</v>
+      </c>
+      <c r="F11" s="22"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="22"/>
       <c r="AC11" s="19"/>
-    </row>
-    <row r="12" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD11" s="19"/>
+    </row>
+    <row r="12" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="19">
         <v>6</v>
       </c>
@@ -4779,33 +4836,36 @@
       <c r="D12" s="21">
         <v>28021957</v>
       </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="19"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="19"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="19"/>
+      <c r="E12" s="27">
+        <v>20191110031</v>
+      </c>
+      <c r="F12" s="22"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="22"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="22"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="22"/>
       <c r="AC12" s="19"/>
-    </row>
-    <row r="13" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD12" s="19"/>
+    </row>
+    <row r="13" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="19">
         <v>7</v>
       </c>
@@ -4818,53 +4878,56 @@
       <c r="D13" s="21">
         <v>29508689</v>
       </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="22">
-        <v>1</v>
-      </c>
-      <c r="H13" s="19"/>
-      <c r="I13" s="23">
-        <v>1</v>
-      </c>
-      <c r="J13" s="19">
-        <v>1</v>
-      </c>
-      <c r="K13" s="22">
-        <v>1</v>
-      </c>
-      <c r="L13" s="19">
-        <v>1</v>
-      </c>
-      <c r="M13" s="22"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="19">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="22">
-        <v>1</v>
-      </c>
-      <c r="T13" s="19"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="19">
-        <v>1</v>
-      </c>
-      <c r="W13" s="22"/>
-      <c r="X13" s="19">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="19">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="19"/>
+      <c r="E13" s="27">
+        <v>20231110055</v>
+      </c>
+      <c r="F13" s="22"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="22">
+        <v>1</v>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="23">
+        <v>1</v>
+      </c>
+      <c r="K13" s="19">
+        <v>1</v>
+      </c>
+      <c r="L13" s="22">
+        <v>1</v>
+      </c>
+      <c r="M13" s="19">
+        <v>1</v>
+      </c>
+      <c r="N13" s="22"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="19">
+        <v>1</v>
+      </c>
+      <c r="R13" s="22"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="22">
+        <v>1</v>
+      </c>
+      <c r="U13" s="19"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="19">
+        <v>1</v>
+      </c>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="22"/>
       <c r="AC13" s="19"/>
-    </row>
-    <row r="14" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD13" s="19"/>
+    </row>
+    <row r="14" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="19">
         <v>8</v>
       </c>
@@ -4877,37 +4940,40 @@
       <c r="D14" s="21">
         <v>30496325</v>
       </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="19">
-        <v>1</v>
-      </c>
-      <c r="I14" s="22"/>
-      <c r="J14" s="19">
-        <v>1</v>
-      </c>
-      <c r="K14" s="22"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="22"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="19"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="19"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="22"/>
-      <c r="X14" s="19"/>
-      <c r="Y14" s="22"/>
-      <c r="Z14" s="19"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="19"/>
+      <c r="E14" s="27">
+        <v>20231110399</v>
+      </c>
+      <c r="F14" s="22"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="19">
+        <v>1</v>
+      </c>
+      <c r="J14" s="22"/>
+      <c r="K14" s="19">
+        <v>1</v>
+      </c>
+      <c r="L14" s="22"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="19"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="19"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="19"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="19"/>
+      <c r="AB14" s="22"/>
       <c r="AC14" s="19"/>
-    </row>
-    <row r="15" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD14" s="19"/>
+    </row>
+    <row r="15" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="19">
         <v>9</v>
       </c>
@@ -4920,49 +4986,52 @@
       <c r="D15" s="21">
         <v>30358773</v>
       </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="19">
+      <c r="E15" s="27">
+        <v>20231110531</v>
+      </c>
+      <c r="F15" s="22"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="19">
         <v>2</v>
       </c>
-      <c r="I15" s="23">
-        <v>1</v>
-      </c>
-      <c r="J15" s="19">
-        <v>1</v>
-      </c>
-      <c r="K15" s="22">
-        <v>1</v>
-      </c>
-      <c r="L15" s="19">
-        <v>1</v>
-      </c>
-      <c r="M15" s="22"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="22"/>
-      <c r="P15" s="19">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="19"/>
-      <c r="S15" s="22">
-        <v>1</v>
-      </c>
-      <c r="T15" s="19"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="19">
-        <v>1</v>
-      </c>
-      <c r="W15" s="22"/>
-      <c r="X15" s="19"/>
-      <c r="Y15" s="22"/>
-      <c r="Z15" s="19"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="19"/>
+      <c r="J15" s="23">
+        <v>1</v>
+      </c>
+      <c r="K15" s="19">
+        <v>1</v>
+      </c>
+      <c r="L15" s="22">
+        <v>1</v>
+      </c>
+      <c r="M15" s="19">
+        <v>1</v>
+      </c>
+      <c r="N15" s="22"/>
+      <c r="O15" s="19"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="19">
+        <v>1</v>
+      </c>
+      <c r="R15" s="22"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="22">
+        <v>1</v>
+      </c>
+      <c r="U15" s="19"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="19">
+        <v>1</v>
+      </c>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="19"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="19"/>
+      <c r="AB15" s="22"/>
       <c r="AC15" s="19"/>
-    </row>
-    <row r="16" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD15" s="19"/>
+    </row>
+    <row r="16" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="19">
         <v>10</v>
       </c>
@@ -4975,33 +5044,36 @@
       <c r="D16" s="21">
         <v>29741760</v>
       </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="19"/>
-      <c r="S16" s="22"/>
-      <c r="T16" s="19"/>
-      <c r="U16" s="22"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="22"/>
-      <c r="X16" s="19"/>
-      <c r="Y16" s="22"/>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="22"/>
-      <c r="AB16" s="19"/>
+      <c r="E16" s="27">
+        <v>20211120003</v>
+      </c>
+      <c r="F16" s="22"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="19"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="19"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="19"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="19"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="19"/>
+      <c r="AB16" s="22"/>
       <c r="AC16" s="19"/>
-    </row>
-    <row r="17" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD16" s="19"/>
+    </row>
+    <row r="17" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="19">
         <v>11</v>
       </c>
@@ -5014,33 +5086,36 @@
       <c r="D17" s="21">
         <v>29983279</v>
       </c>
-      <c r="E17" s="22"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="22"/>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="22"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="19"/>
+      <c r="E17" s="27">
+        <v>20231110841</v>
+      </c>
+      <c r="F17" s="22"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="19"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="19"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="19"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="19"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="19"/>
+      <c r="AB17" s="22"/>
       <c r="AC17" s="19"/>
-    </row>
-    <row r="18" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD17" s="19"/>
+    </row>
+    <row r="18" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="19">
         <v>12</v>
       </c>
@@ -5053,33 +5128,36 @@
       <c r="D18" s="21">
         <v>30497244</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="22"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="22"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="22"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="22"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="19"/>
+      <c r="E18" s="27">
+        <v>20231110111</v>
+      </c>
+      <c r="F18" s="22"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="19"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="19"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="19"/>
+      <c r="X18" s="22"/>
+      <c r="Y18" s="19"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="19"/>
+      <c r="AB18" s="22"/>
       <c r="AC18" s="19"/>
-    </row>
-    <row r="19" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD18" s="19"/>
+    </row>
+    <row r="19" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="19">
         <v>13</v>
       </c>
@@ -5092,33 +5170,36 @@
       <c r="D19" s="21">
         <v>30030632</v>
       </c>
-      <c r="E19" s="22"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="22"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="22"/>
-      <c r="T19" s="19"/>
-      <c r="U19" s="22"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="22"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="22"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="22"/>
-      <c r="AB19" s="19"/>
+      <c r="E19" s="27">
+        <v>20221110010</v>
+      </c>
+      <c r="F19" s="22"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="19"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="19"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="19"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="19"/>
+      <c r="T19" s="22"/>
+      <c r="U19" s="19"/>
+      <c r="V19" s="22"/>
+      <c r="W19" s="19"/>
+      <c r="X19" s="22"/>
+      <c r="Y19" s="19"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="19"/>
+      <c r="AB19" s="22"/>
       <c r="AC19" s="19"/>
-    </row>
-    <row r="20" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD19" s="19"/>
+    </row>
+    <row r="20" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="19">
         <v>14</v>
       </c>
@@ -5131,41 +5212,44 @@
       <c r="D20" s="21">
         <v>30579903</v>
       </c>
-      <c r="E20" s="22"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="22">
-        <v>1</v>
-      </c>
-      <c r="H20" s="19"/>
-      <c r="I20" s="23">
-        <v>1</v>
-      </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="19">
-        <v>1</v>
-      </c>
-      <c r="O20" s="22"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="22"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="22"/>
-      <c r="T20" s="19"/>
-      <c r="U20" s="22">
-        <v>1</v>
-      </c>
-      <c r="V20" s="19"/>
-      <c r="W20" s="22"/>
-      <c r="X20" s="19"/>
-      <c r="Y20" s="22"/>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="22"/>
-      <c r="AB20" s="19"/>
+      <c r="E20" s="27">
+        <v>20231110114</v>
+      </c>
+      <c r="F20" s="22"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="22">
+        <v>1</v>
+      </c>
+      <c r="I20" s="19"/>
+      <c r="J20" s="23">
+        <v>1</v>
+      </c>
+      <c r="K20" s="19"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="19">
+        <v>1</v>
+      </c>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="19"/>
+      <c r="T20" s="22"/>
+      <c r="U20" s="19"/>
+      <c r="V20" s="22">
+        <v>1</v>
+      </c>
+      <c r="W20" s="19"/>
+      <c r="X20" s="22"/>
+      <c r="Y20" s="19"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="19"/>
+      <c r="AB20" s="22"/>
       <c r="AC20" s="19"/>
-    </row>
-    <row r="21" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD20" s="19"/>
+    </row>
+    <row r="21" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="19">
         <v>15</v>
       </c>
@@ -5178,35 +5262,38 @@
       <c r="D21" s="21">
         <v>31065516</v>
       </c>
-      <c r="E21" s="22"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="22">
-        <v>1</v>
-      </c>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="22"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="22"/>
-      <c r="T21" s="19"/>
-      <c r="U21" s="22"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="22"/>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="22"/>
-      <c r="Z21" s="19"/>
-      <c r="AA21" s="22"/>
-      <c r="AB21" s="19"/>
+      <c r="E21" s="27">
+        <v>20231110454</v>
+      </c>
+      <c r="F21" s="22"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="22"/>
+      <c r="S21" s="19"/>
+      <c r="T21" s="22"/>
+      <c r="U21" s="19"/>
+      <c r="V21" s="22"/>
+      <c r="W21" s="19"/>
+      <c r="X21" s="22"/>
+      <c r="Y21" s="19"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="19"/>
+      <c r="AB21" s="22"/>
       <c r="AC21" s="19"/>
-    </row>
-    <row r="22" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD21" s="19"/>
+    </row>
+    <row r="22" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="19">
         <v>16</v>
       </c>
@@ -5219,33 +5306,34 @@
       <c r="D22" s="21">
         <v>28127331</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="22"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="22"/>
-      <c r="T22" s="19"/>
-      <c r="U22" s="22"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="22"/>
-      <c r="X22" s="19"/>
-      <c r="Y22" s="22"/>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="19"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="22"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="22"/>
+      <c r="U22" s="19"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="19"/>
+      <c r="X22" s="22"/>
+      <c r="Y22" s="19"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="19"/>
+      <c r="AB22" s="22"/>
       <c r="AC22" s="19"/>
-    </row>
-    <row r="23" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD22" s="19"/>
+    </row>
+    <row r="23" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="19">
         <v>17</v>
       </c>
@@ -5258,43 +5346,46 @@
       <c r="D23" s="21">
         <v>30157257</v>
       </c>
-      <c r="E23" s="22">
-        <v>1</v>
-      </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="22">
-        <v>1</v>
-      </c>
-      <c r="H23" s="19"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="22">
-        <v>1</v>
-      </c>
-      <c r="L23" s="19">
-        <v>1</v>
-      </c>
-      <c r="M23" s="22"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="22"/>
-      <c r="T23" s="19"/>
-      <c r="U23" s="22">
-        <v>1</v>
-      </c>
-      <c r="V23" s="19"/>
-      <c r="W23" s="22"/>
-      <c r="X23" s="19"/>
-      <c r="Y23" s="22"/>
-      <c r="Z23" s="19"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="19"/>
+      <c r="E23" s="27">
+        <v>20221110657</v>
+      </c>
+      <c r="F23" s="22">
+        <v>1</v>
+      </c>
+      <c r="G23" s="19"/>
+      <c r="H23" s="22">
+        <v>1</v>
+      </c>
+      <c r="I23" s="19"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="22">
+        <v>1</v>
+      </c>
+      <c r="M23" s="19">
+        <v>1</v>
+      </c>
+      <c r="N23" s="22"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="22"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="22"/>
+      <c r="U23" s="19"/>
+      <c r="V23" s="22">
+        <v>1</v>
+      </c>
+      <c r="W23" s="19"/>
+      <c r="X23" s="22"/>
+      <c r="Y23" s="19"/>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="19"/>
+      <c r="AB23" s="22"/>
       <c r="AC23" s="19"/>
-    </row>
-    <row r="24" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD23" s="19"/>
+    </row>
+    <row r="24" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="19">
         <v>18</v>
       </c>
@@ -5307,35 +5398,40 @@
       <c r="D24" s="21">
         <v>25736710</v>
       </c>
-      <c r="E24" s="22"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="19">
-        <v>1</v>
-      </c>
-      <c r="I24" s="22"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="22"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="22"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="22"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="22"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="22"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="22"/>
-      <c r="AB24" s="19"/>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>20161110446</t>
+        </is>
+      </c>
+      <c r="F24" s="22"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="19">
+        <v>1</v>
+      </c>
+      <c r="J24" s="22"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="22"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="22"/>
+      <c r="U24" s="19"/>
+      <c r="V24" s="22"/>
+      <c r="W24" s="19"/>
+      <c r="X24" s="22"/>
+      <c r="Y24" s="19"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="19"/>
+      <c r="AB24" s="22"/>
       <c r="AC24" s="19"/>
-    </row>
-    <row r="25" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD24" s="19"/>
+    </row>
+    <row r="25" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="19">
         <v>19</v>
       </c>
@@ -5348,33 +5444,38 @@
       <c r="D25" s="21">
         <v>29506315</v>
       </c>
-      <c r="E25" s="22"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="19"/>
-      <c r="S25" s="22"/>
-      <c r="T25" s="19"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="19"/>
-      <c r="W25" s="22"/>
-      <c r="X25" s="19"/>
-      <c r="Y25" s="22"/>
-      <c r="Z25" s="19"/>
-      <c r="AA25" s="22"/>
-      <c r="AB25" s="19"/>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>20211110506</t>
+        </is>
+      </c>
+      <c r="F25" s="22"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="22"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="22"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="22"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="22"/>
+      <c r="Y25" s="19"/>
+      <c r="Z25" s="22"/>
+      <c r="AA25" s="19"/>
+      <c r="AB25" s="22"/>
       <c r="AC25" s="19"/>
-    </row>
-    <row r="26" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD25" s="19"/>
+    </row>
+    <row r="26" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="19">
         <v>20</v>
       </c>
@@ -5387,33 +5488,38 @@
       <c r="D26" s="21">
         <v>29662587</v>
       </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="19"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="22"/>
-      <c r="R26" s="19"/>
-      <c r="S26" s="22"/>
-      <c r="T26" s="19"/>
-      <c r="U26" s="22"/>
-      <c r="V26" s="19"/>
-      <c r="W26" s="22"/>
-      <c r="X26" s="19"/>
-      <c r="Y26" s="22"/>
-      <c r="Z26" s="19"/>
-      <c r="AA26" s="22"/>
-      <c r="AB26" s="19"/>
+      <c r="E26" s="27" t="inlineStr">
+        <is>
+          <t>20211110471</t>
+        </is>
+      </c>
+      <c r="F26" s="22"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="22"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="22"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="22"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="22"/>
+      <c r="Y26" s="19"/>
+      <c r="Z26" s="22"/>
+      <c r="AA26" s="19"/>
+      <c r="AB26" s="22"/>
       <c r="AC26" s="19"/>
-    </row>
-    <row r="27" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD26" s="19"/>
+    </row>
+    <row r="27" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="19">
         <v>21</v>
       </c>
@@ -5426,33 +5532,38 @@
       <c r="D27" s="21">
         <v>28462135</v>
       </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="19"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="22"/>
-      <c r="T27" s="19"/>
-      <c r="U27" s="22"/>
-      <c r="V27" s="19"/>
-      <c r="W27" s="22"/>
-      <c r="X27" s="19"/>
-      <c r="Y27" s="22"/>
-      <c r="Z27" s="19"/>
-      <c r="AA27" s="22"/>
-      <c r="AB27" s="19"/>
+      <c r="E27" s="27" t="inlineStr">
+        <is>
+          <t>20191120013</t>
+        </is>
+      </c>
+      <c r="F27" s="22"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="22"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="22"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="22"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="22"/>
+      <c r="Y27" s="19"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="19"/>
+      <c r="AB27" s="22"/>
       <c r="AC27" s="19"/>
-    </row>
-    <row r="28" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD27" s="19"/>
+    </row>
+    <row r="28" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="19">
         <v>22</v>
       </c>
@@ -5465,35 +5576,40 @@
       <c r="D28" s="21">
         <v>26895167</v>
       </c>
-      <c r="E28" s="22"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="19">
-        <v>1</v>
-      </c>
-      <c r="K28" s="22"/>
-      <c r="L28" s="19"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="19"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="19"/>
-      <c r="S28" s="22"/>
-      <c r="T28" s="19"/>
-      <c r="U28" s="22"/>
-      <c r="V28" s="19"/>
-      <c r="W28" s="22"/>
-      <c r="X28" s="19"/>
-      <c r="Y28" s="22"/>
-      <c r="Z28" s="19"/>
-      <c r="AA28" s="22"/>
-      <c r="AB28" s="19"/>
+      <c r="E28" s="27" t="inlineStr">
+        <is>
+          <t>20181110067</t>
+        </is>
+      </c>
+      <c r="F28" s="22"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="19">
+        <v>1</v>
+      </c>
+      <c r="L28" s="22"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="22"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="22"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="22"/>
+      <c r="Y28" s="19"/>
+      <c r="Z28" s="22"/>
+      <c r="AA28" s="19"/>
+      <c r="AB28" s="22"/>
       <c r="AC28" s="19"/>
-    </row>
-    <row r="29" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD28" s="19"/>
+    </row>
+    <row r="29" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="19">
         <v>23</v>
       </c>
@@ -5506,35 +5622,40 @@
       <c r="D29" s="21">
         <v>30727488</v>
       </c>
-      <c r="E29" s="22">
-        <v>1</v>
-      </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="22"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="22"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="22"/>
-      <c r="R29" s="19"/>
-      <c r="S29" s="22"/>
-      <c r="T29" s="19"/>
-      <c r="U29" s="22"/>
-      <c r="V29" s="19"/>
-      <c r="W29" s="22"/>
-      <c r="X29" s="19"/>
-      <c r="Y29" s="22"/>
-      <c r="Z29" s="19"/>
-      <c r="AA29" s="22"/>
-      <c r="AB29" s="19"/>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>20231110234</t>
+        </is>
+      </c>
+      <c r="F29" s="22">
+        <v>1</v>
+      </c>
+      <c r="G29" s="19"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="19"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="19"/>
+      <c r="R29" s="22"/>
+      <c r="S29" s="19"/>
+      <c r="T29" s="22"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="22"/>
+      <c r="W29" s="19"/>
+      <c r="X29" s="22"/>
+      <c r="Y29" s="19"/>
+      <c r="Z29" s="22"/>
+      <c r="AA29" s="19"/>
+      <c r="AB29" s="22"/>
       <c r="AC29" s="19"/>
-    </row>
-    <row r="30" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD29" s="19"/>
+    </row>
+    <row r="30" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="19">
         <v>24</v>
       </c>
@@ -5547,33 +5668,38 @@
       <c r="D30" s="21">
         <v>30821945</v>
       </c>
-      <c r="E30" s="22"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="19"/>
-      <c r="M30" s="22"/>
-      <c r="N30" s="19"/>
-      <c r="O30" s="22"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="22"/>
-      <c r="R30" s="19"/>
-      <c r="S30" s="22"/>
-      <c r="T30" s="19"/>
-      <c r="U30" s="22"/>
-      <c r="V30" s="19"/>
-      <c r="W30" s="22"/>
-      <c r="X30" s="19"/>
-      <c r="Y30" s="22"/>
-      <c r="Z30" s="19"/>
-      <c r="AA30" s="22"/>
-      <c r="AB30" s="19"/>
+      <c r="E30" s="27" t="inlineStr">
+        <is>
+          <t>20231110297</t>
+        </is>
+      </c>
+      <c r="F30" s="22"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="19"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="19"/>
+      <c r="R30" s="22"/>
+      <c r="S30" s="19"/>
+      <c r="T30" s="22"/>
+      <c r="U30" s="19"/>
+      <c r="V30" s="22"/>
+      <c r="W30" s="19"/>
+      <c r="X30" s="22"/>
+      <c r="Y30" s="19"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="19"/>
+      <c r="AB30" s="22"/>
       <c r="AC30" s="19"/>
-    </row>
-    <row r="31" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD30" s="19"/>
+    </row>
+    <row r="31" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="19">
         <v>25</v>
       </c>
@@ -5586,33 +5712,38 @@
       <c r="D31" s="21">
         <v>30330786</v>
       </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="19"/>
-      <c r="M31" s="22"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="22"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="22"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="22"/>
-      <c r="T31" s="19"/>
-      <c r="U31" s="22"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="22"/>
-      <c r="X31" s="19"/>
-      <c r="Y31" s="22"/>
-      <c r="Z31" s="19"/>
-      <c r="AA31" s="22"/>
-      <c r="AB31" s="19"/>
+      <c r="E31" s="27" t="inlineStr">
+        <is>
+          <t>20231110059</t>
+        </is>
+      </c>
+      <c r="F31" s="22"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="19"/>
+      <c r="R31" s="22"/>
+      <c r="S31" s="19"/>
+      <c r="T31" s="22"/>
+      <c r="U31" s="19"/>
+      <c r="V31" s="22"/>
+      <c r="W31" s="19"/>
+      <c r="X31" s="22"/>
+      <c r="Y31" s="19"/>
+      <c r="Z31" s="22"/>
+      <c r="AA31" s="19"/>
+      <c r="AB31" s="22"/>
       <c r="AC31" s="19"/>
-    </row>
-    <row r="32" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD31" s="19"/>
+    </row>
+    <row r="32" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="19">
         <v>26</v>
       </c>
@@ -5625,35 +5756,40 @@
       <c r="D32" s="21">
         <v>29850491</v>
       </c>
-      <c r="E32" s="22"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="22">
-        <v>1</v>
-      </c>
-      <c r="H32" s="19"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="19"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="19"/>
-      <c r="O32" s="22"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="22"/>
-      <c r="R32" s="19"/>
-      <c r="S32" s="22"/>
-      <c r="T32" s="19"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="19"/>
-      <c r="W32" s="22"/>
-      <c r="X32" s="19"/>
-      <c r="Y32" s="22"/>
-      <c r="Z32" s="19"/>
-      <c r="AA32" s="22"/>
-      <c r="AB32" s="19"/>
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>20221110100</t>
+        </is>
+      </c>
+      <c r="F32" s="22"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="22">
+        <v>1</v>
+      </c>
+      <c r="I32" s="19"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="19"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="19"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="19"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="19"/>
+      <c r="V32" s="22"/>
+      <c r="W32" s="19"/>
+      <c r="X32" s="22"/>
+      <c r="Y32" s="19"/>
+      <c r="Z32" s="22"/>
+      <c r="AA32" s="19"/>
+      <c r="AB32" s="22"/>
       <c r="AC32" s="19"/>
-    </row>
-    <row r="33" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD32" s="19"/>
+    </row>
+    <row r="33" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="19">
         <v>27</v>
       </c>
@@ -5666,33 +5802,38 @@
       <c r="D33" s="21">
         <v>30751145</v>
       </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="22"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="22"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="22"/>
-      <c r="T33" s="19"/>
-      <c r="U33" s="22"/>
-      <c r="V33" s="19"/>
-      <c r="W33" s="22"/>
-      <c r="X33" s="19"/>
-      <c r="Y33" s="22"/>
-      <c r="Z33" s="19"/>
-      <c r="AA33" s="22"/>
-      <c r="AB33" s="19"/>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>20231110519</t>
+        </is>
+      </c>
+      <c r="F33" s="22"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="22"/>
+      <c r="S33" s="19"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="19"/>
+      <c r="V33" s="22"/>
+      <c r="W33" s="19"/>
+      <c r="X33" s="22"/>
+      <c r="Y33" s="19"/>
+      <c r="Z33" s="22"/>
+      <c r="AA33" s="19"/>
+      <c r="AB33" s="22"/>
       <c r="AC33" s="19"/>
-    </row>
-    <row r="34" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD33" s="19"/>
+    </row>
+    <row r="34" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="19">
         <v>28</v>
       </c>
@@ -5705,33 +5846,38 @@
       <c r="D34" s="21">
         <v>30612944</v>
       </c>
-      <c r="E34" s="22"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="19"/>
-      <c r="M34" s="22"/>
-      <c r="N34" s="19"/>
-      <c r="O34" s="22"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="22"/>
-      <c r="R34" s="19"/>
-      <c r="S34" s="22"/>
-      <c r="T34" s="19"/>
-      <c r="U34" s="22"/>
-      <c r="V34" s="19"/>
-      <c r="W34" s="22"/>
-      <c r="X34" s="19"/>
-      <c r="Y34" s="22"/>
-      <c r="Z34" s="19"/>
-      <c r="AA34" s="22"/>
-      <c r="AB34" s="19"/>
+      <c r="E34" s="27" t="inlineStr">
+        <is>
+          <t>20231110217</t>
+        </is>
+      </c>
+      <c r="F34" s="22"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="22"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="22"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="22"/>
+      <c r="U34" s="19"/>
+      <c r="V34" s="22"/>
+      <c r="W34" s="19"/>
+      <c r="X34" s="22"/>
+      <c r="Y34" s="19"/>
+      <c r="Z34" s="22"/>
+      <c r="AA34" s="19"/>
+      <c r="AB34" s="22"/>
       <c r="AC34" s="19"/>
-    </row>
-    <row r="35" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD34" s="19"/>
+    </row>
+    <row r="35" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="19">
         <v>29</v>
       </c>
@@ -5744,33 +5890,38 @@
       <c r="D35" s="21">
         <v>29677861</v>
       </c>
-      <c r="E35" s="22"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="19"/>
-      <c r="O35" s="22"/>
-      <c r="P35" s="19"/>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="19"/>
-      <c r="S35" s="22"/>
-      <c r="T35" s="19"/>
-      <c r="U35" s="22"/>
-      <c r="V35" s="19"/>
-      <c r="W35" s="22"/>
-      <c r="X35" s="19"/>
-      <c r="Y35" s="22"/>
-      <c r="Z35" s="19"/>
-      <c r="AA35" s="22"/>
-      <c r="AB35" s="19"/>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>20211120097</t>
+        </is>
+      </c>
+      <c r="F35" s="22"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="19"/>
+      <c r="R35" s="22"/>
+      <c r="S35" s="19"/>
+      <c r="T35" s="22"/>
+      <c r="U35" s="19"/>
+      <c r="V35" s="22"/>
+      <c r="W35" s="19"/>
+      <c r="X35" s="22"/>
+      <c r="Y35" s="19"/>
+      <c r="Z35" s="22"/>
+      <c r="AA35" s="19"/>
+      <c r="AB35" s="22"/>
       <c r="AC35" s="19"/>
-    </row>
-    <row r="36" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD35" s="19"/>
+    </row>
+    <row r="36" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="19">
         <v>30</v>
       </c>
@@ -5783,33 +5934,38 @@
       <c r="D36" s="21">
         <v>29661990</v>
       </c>
-      <c r="E36" s="22"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="22"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="22"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="22"/>
-      <c r="R36" s="19"/>
-      <c r="S36" s="22"/>
-      <c r="T36" s="19"/>
-      <c r="U36" s="22"/>
-      <c r="V36" s="19"/>
-      <c r="W36" s="22"/>
-      <c r="X36" s="19"/>
-      <c r="Y36" s="22"/>
-      <c r="Z36" s="19"/>
-      <c r="AA36" s="22"/>
-      <c r="AB36" s="19"/>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>20231110045</t>
+        </is>
+      </c>
+      <c r="F36" s="22"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="22"/>
+      <c r="S36" s="19"/>
+      <c r="T36" s="22"/>
+      <c r="U36" s="19"/>
+      <c r="V36" s="22"/>
+      <c r="W36" s="19"/>
+      <c r="X36" s="22"/>
+      <c r="Y36" s="19"/>
+      <c r="Z36" s="22"/>
+      <c r="AA36" s="19"/>
+      <c r="AB36" s="22"/>
       <c r="AC36" s="19"/>
-    </row>
-    <row r="37" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD36" s="19"/>
+    </row>
+    <row r="37" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="19">
         <v>31</v>
       </c>
@@ -5822,33 +5978,38 @@
       <c r="D37" s="21">
         <v>27472721</v>
       </c>
-      <c r="E37" s="22"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="19"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="22"/>
-      <c r="P37" s="19"/>
-      <c r="Q37" s="22"/>
-      <c r="R37" s="19"/>
-      <c r="S37" s="22"/>
-      <c r="T37" s="19"/>
-      <c r="U37" s="22"/>
-      <c r="V37" s="19"/>
-      <c r="W37" s="22"/>
-      <c r="X37" s="19"/>
-      <c r="Y37" s="22"/>
-      <c r="Z37" s="19"/>
-      <c r="AA37" s="22"/>
-      <c r="AB37" s="19"/>
+      <c r="E37" s="27" t="inlineStr">
+        <is>
+          <t>20191110253</t>
+        </is>
+      </c>
+      <c r="F37" s="22"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="19"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="19"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="19"/>
+      <c r="R37" s="22"/>
+      <c r="S37" s="19"/>
+      <c r="T37" s="22"/>
+      <c r="U37" s="19"/>
+      <c r="V37" s="22"/>
+      <c r="W37" s="19"/>
+      <c r="X37" s="22"/>
+      <c r="Y37" s="19"/>
+      <c r="Z37" s="22"/>
+      <c r="AA37" s="19"/>
+      <c r="AB37" s="22"/>
       <c r="AC37" s="19"/>
-    </row>
-    <row r="38" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD37" s="19"/>
+    </row>
+    <row r="38" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="19">
         <v>32</v>
       </c>
@@ -5861,33 +6022,38 @@
       <c r="D38" s="21">
         <v>29887224</v>
       </c>
-      <c r="E38" s="22"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="22"/>
-      <c r="N38" s="19"/>
-      <c r="O38" s="22"/>
-      <c r="P38" s="19"/>
-      <c r="Q38" s="22"/>
-      <c r="R38" s="19"/>
-      <c r="S38" s="22"/>
-      <c r="T38" s="19"/>
-      <c r="U38" s="22"/>
-      <c r="V38" s="19"/>
-      <c r="W38" s="22"/>
-      <c r="X38" s="19"/>
-      <c r="Y38" s="22"/>
-      <c r="Z38" s="19"/>
-      <c r="AA38" s="22"/>
-      <c r="AB38" s="19"/>
+      <c r="E38" s="27" t="inlineStr">
+        <is>
+          <t>20221110599</t>
+        </is>
+      </c>
+      <c r="F38" s="22"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="19"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="19"/>
+      <c r="R38" s="22"/>
+      <c r="S38" s="19"/>
+      <c r="T38" s="22"/>
+      <c r="U38" s="19"/>
+      <c r="V38" s="22"/>
+      <c r="W38" s="19"/>
+      <c r="X38" s="22"/>
+      <c r="Y38" s="19"/>
+      <c r="Z38" s="22"/>
+      <c r="AA38" s="19"/>
+      <c r="AB38" s="22"/>
       <c r="AC38" s="19"/>
-    </row>
-    <row r="39" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD38" s="19"/>
+    </row>
+    <row r="39" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="19">
         <v>33</v>
       </c>
@@ -5900,33 +6066,38 @@
       <c r="D39" s="21">
         <v>28317519</v>
       </c>
-      <c r="E39" s="22"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="22"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="22"/>
-      <c r="P39" s="19"/>
-      <c r="Q39" s="22"/>
-      <c r="R39" s="19"/>
-      <c r="S39" s="22"/>
-      <c r="T39" s="19"/>
-      <c r="U39" s="22"/>
-      <c r="V39" s="19"/>
-      <c r="W39" s="22"/>
-      <c r="X39" s="19"/>
-      <c r="Y39" s="22"/>
-      <c r="Z39" s="19"/>
-      <c r="AA39" s="22"/>
-      <c r="AB39" s="19"/>
+      <c r="E39" s="27" t="inlineStr">
+        <is>
+          <t>20191110269</t>
+        </is>
+      </c>
+      <c r="F39" s="22"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="22"/>
+      <c r="Q39" s="19"/>
+      <c r="R39" s="22"/>
+      <c r="S39" s="19"/>
+      <c r="T39" s="22"/>
+      <c r="U39" s="19"/>
+      <c r="V39" s="22"/>
+      <c r="W39" s="19"/>
+      <c r="X39" s="22"/>
+      <c r="Y39" s="19"/>
+      <c r="Z39" s="22"/>
+      <c r="AA39" s="19"/>
+      <c r="AB39" s="22"/>
       <c r="AC39" s="19"/>
-    </row>
-    <row r="40" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD39" s="19"/>
+    </row>
+    <row r="40" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="19">
         <v>34</v>
       </c>
@@ -5939,37 +6110,42 @@
       <c r="D40" s="21">
         <v>30496487</v>
       </c>
-      <c r="E40" s="22">
-        <v>1</v>
-      </c>
-      <c r="F40" s="19"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="22"/>
-      <c r="J40" s="19">
-        <v>1</v>
-      </c>
-      <c r="K40" s="22"/>
-      <c r="L40" s="19"/>
-      <c r="M40" s="22"/>
-      <c r="N40" s="19"/>
-      <c r="O40" s="22"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="22"/>
-      <c r="R40" s="19"/>
-      <c r="S40" s="22"/>
-      <c r="T40" s="19"/>
-      <c r="U40" s="22"/>
-      <c r="V40" s="19"/>
-      <c r="W40" s="22"/>
-      <c r="X40" s="19"/>
-      <c r="Y40" s="22"/>
-      <c r="Z40" s="19"/>
-      <c r="AA40" s="22"/>
-      <c r="AB40" s="19"/>
+      <c r="E40" s="27" t="inlineStr">
+        <is>
+          <t>20231110123</t>
+        </is>
+      </c>
+      <c r="F40" s="22">
+        <v>1</v>
+      </c>
+      <c r="G40" s="19"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="19">
+        <v>1</v>
+      </c>
+      <c r="L40" s="22"/>
+      <c r="M40" s="19"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="22"/>
+      <c r="Q40" s="19"/>
+      <c r="R40" s="22"/>
+      <c r="S40" s="19"/>
+      <c r="T40" s="22"/>
+      <c r="U40" s="19"/>
+      <c r="V40" s="22"/>
+      <c r="W40" s="19"/>
+      <c r="X40" s="22"/>
+      <c r="Y40" s="19"/>
+      <c r="Z40" s="22"/>
+      <c r="AA40" s="19"/>
+      <c r="AB40" s="22"/>
       <c r="AC40" s="19"/>
-    </row>
-    <row r="41" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD40" s="19"/>
+    </row>
+    <row r="41" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="19">
         <v>35</v>
       </c>
@@ -5982,39 +6158,44 @@
       <c r="D41" s="21">
         <v>30411279</v>
       </c>
-      <c r="E41" s="22">
-        <v>1</v>
-      </c>
-      <c r="F41" s="19"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="19">
-        <v>1</v>
-      </c>
-      <c r="I41" s="23">
-        <v>1</v>
-      </c>
-      <c r="J41" s="19"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="19"/>
-      <c r="M41" s="22"/>
-      <c r="N41" s="19"/>
-      <c r="O41" s="22"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="22"/>
-      <c r="R41" s="19"/>
-      <c r="S41" s="22"/>
-      <c r="T41" s="19"/>
-      <c r="U41" s="22"/>
-      <c r="V41" s="19"/>
-      <c r="W41" s="22"/>
-      <c r="X41" s="19"/>
-      <c r="Y41" s="22"/>
-      <c r="Z41" s="19"/>
-      <c r="AA41" s="22"/>
-      <c r="AB41" s="19"/>
+      <c r="E41" s="27" t="inlineStr">
+        <is>
+          <t>20221110183</t>
+        </is>
+      </c>
+      <c r="F41" s="22">
+        <v>1</v>
+      </c>
+      <c r="G41" s="19"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="19">
+        <v>1</v>
+      </c>
+      <c r="J41" s="23">
+        <v>1</v>
+      </c>
+      <c r="K41" s="19"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="19"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="19"/>
+      <c r="P41" s="22"/>
+      <c r="Q41" s="19"/>
+      <c r="R41" s="22"/>
+      <c r="S41" s="19"/>
+      <c r="T41" s="22"/>
+      <c r="U41" s="19"/>
+      <c r="V41" s="22"/>
+      <c r="W41" s="19"/>
+      <c r="X41" s="22"/>
+      <c r="Y41" s="19"/>
+      <c r="Z41" s="22"/>
+      <c r="AA41" s="19"/>
+      <c r="AB41" s="22"/>
       <c r="AC41" s="19"/>
-    </row>
-    <row r="42" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD41" s="19"/>
+    </row>
+    <row r="42" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="19">
         <v>36</v>
       </c>
@@ -6027,35 +6208,40 @@
       <c r="D42" s="21">
         <v>26783022</v>
       </c>
-      <c r="E42" s="22"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="19">
-        <v>1</v>
-      </c>
-      <c r="I42" s="22"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="22"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="22"/>
-      <c r="N42" s="19"/>
-      <c r="O42" s="22"/>
-      <c r="P42" s="19"/>
-      <c r="Q42" s="22"/>
-      <c r="R42" s="19"/>
-      <c r="S42" s="22"/>
-      <c r="T42" s="19"/>
-      <c r="U42" s="22"/>
-      <c r="V42" s="19"/>
-      <c r="W42" s="22"/>
-      <c r="X42" s="19"/>
-      <c r="Y42" s="22"/>
-      <c r="Z42" s="19"/>
-      <c r="AA42" s="22"/>
-      <c r="AB42" s="19"/>
+      <c r="E42" s="27" t="inlineStr">
+        <is>
+          <t>20171110314</t>
+        </is>
+      </c>
+      <c r="F42" s="22"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="19">
+        <v>1</v>
+      </c>
+      <c r="J42" s="22"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="19"/>
+      <c r="P42" s="22"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="22"/>
+      <c r="S42" s="19"/>
+      <c r="T42" s="22"/>
+      <c r="U42" s="19"/>
+      <c r="V42" s="22"/>
+      <c r="W42" s="19"/>
+      <c r="X42" s="22"/>
+      <c r="Y42" s="19"/>
+      <c r="Z42" s="22"/>
+      <c r="AA42" s="19"/>
+      <c r="AB42" s="22"/>
       <c r="AC42" s="19"/>
-    </row>
-    <row r="43" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD42" s="19"/>
+    </row>
+    <row r="43" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="19">
         <v>37</v>
       </c>
@@ -6068,33 +6254,38 @@
       <c r="D43" s="21">
         <v>31460153</v>
       </c>
-      <c r="E43" s="22"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="22"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="22"/>
-      <c r="N43" s="19"/>
-      <c r="O43" s="22"/>
-      <c r="P43" s="19"/>
-      <c r="Q43" s="22"/>
-      <c r="R43" s="19"/>
-      <c r="S43" s="22"/>
-      <c r="T43" s="19"/>
-      <c r="U43" s="22"/>
-      <c r="V43" s="19"/>
-      <c r="W43" s="22"/>
-      <c r="X43" s="19"/>
-      <c r="Y43" s="22"/>
-      <c r="Z43" s="19"/>
-      <c r="AA43" s="22"/>
-      <c r="AB43" s="19"/>
+      <c r="E43" s="27" t="inlineStr">
+        <is>
+          <t>20231110506</t>
+        </is>
+      </c>
+      <c r="F43" s="22"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="22"/>
+      <c r="O43" s="19"/>
+      <c r="P43" s="22"/>
+      <c r="Q43" s="19"/>
+      <c r="R43" s="22"/>
+      <c r="S43" s="19"/>
+      <c r="T43" s="22"/>
+      <c r="U43" s="19"/>
+      <c r="V43" s="22"/>
+      <c r="W43" s="19"/>
+      <c r="X43" s="22"/>
+      <c r="Y43" s="19"/>
+      <c r="Z43" s="22"/>
+      <c r="AA43" s="19"/>
+      <c r="AB43" s="22"/>
       <c r="AC43" s="19"/>
-    </row>
-    <row r="44" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD43" s="19"/>
+    </row>
+    <row r="44" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="19">
         <v>38</v>
       </c>
@@ -6107,55 +6298,60 @@
       <c r="D44" s="21">
         <v>26994959</v>
       </c>
-      <c r="E44" s="22">
-        <v>1</v>
-      </c>
-      <c r="F44" s="19"/>
-      <c r="G44" s="22">
-        <v>1</v>
-      </c>
-      <c r="H44" s="19">
-        <v>1</v>
-      </c>
-      <c r="I44" s="23">
-        <v>1</v>
-      </c>
-      <c r="J44" s="19">
-        <v>1</v>
-      </c>
-      <c r="K44" s="22"/>
-      <c r="L44" s="19"/>
-      <c r="M44" s="22"/>
-      <c r="N44" s="19">
-        <v>1</v>
-      </c>
-      <c r="O44" s="22"/>
-      <c r="P44" s="19"/>
-      <c r="Q44" s="22"/>
-      <c r="R44" s="19">
+      <c r="E44" s="27" t="inlineStr">
+        <is>
+          <t>20191110582</t>
+        </is>
+      </c>
+      <c r="F44" s="22">
+        <v>1</v>
+      </c>
+      <c r="G44" s="19"/>
+      <c r="H44" s="22">
+        <v>1</v>
+      </c>
+      <c r="I44" s="19">
+        <v>1</v>
+      </c>
+      <c r="J44" s="23">
+        <v>1</v>
+      </c>
+      <c r="K44" s="19">
+        <v>1</v>
+      </c>
+      <c r="L44" s="22"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="19">
+        <v>1</v>
+      </c>
+      <c r="P44" s="22"/>
+      <c r="Q44" s="19"/>
+      <c r="R44" s="22"/>
+      <c r="S44" s="19">
         <v>2</v>
       </c>
-      <c r="S44" s="22">
-        <v>1</v>
-      </c>
-      <c r="T44" s="19"/>
-      <c r="U44" s="22"/>
-      <c r="V44" s="19">
-        <v>1</v>
-      </c>
-      <c r="W44" s="22"/>
-      <c r="X44" s="19">
-        <v>1</v>
-      </c>
-      <c r="Y44" s="22"/>
-      <c r="Z44" s="19">
-        <v>1</v>
-      </c>
-      <c r="AA44" s="22"/>
-      <c r="AB44" s="19"/>
+      <c r="T44" s="22">
+        <v>1</v>
+      </c>
+      <c r="U44" s="19"/>
+      <c r="V44" s="22"/>
+      <c r="W44" s="19">
+        <v>1</v>
+      </c>
+      <c r="X44" s="22"/>
+      <c r="Y44" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="22"/>
+      <c r="AA44" s="19">
+        <v>1</v>
+      </c>
+      <c r="AB44" s="22"/>
       <c r="AC44" s="19"/>
-    </row>
-    <row r="45" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD44" s="19"/>
+    </row>
+    <row r="45" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="19">
         <v>39</v>
       </c>
@@ -6168,35 +6364,40 @@
       <c r="D45" s="21">
         <v>30370768</v>
       </c>
-      <c r="E45" s="22"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="19">
-        <v>1</v>
-      </c>
-      <c r="K45" s="22"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="22"/>
-      <c r="N45" s="19"/>
-      <c r="O45" s="22"/>
-      <c r="P45" s="19"/>
-      <c r="Q45" s="22"/>
-      <c r="R45" s="19"/>
-      <c r="S45" s="22"/>
-      <c r="T45" s="19"/>
-      <c r="U45" s="22"/>
-      <c r="V45" s="19"/>
-      <c r="W45" s="22"/>
-      <c r="X45" s="19"/>
-      <c r="Y45" s="22"/>
-      <c r="Z45" s="19"/>
-      <c r="AA45" s="22"/>
-      <c r="AB45" s="19"/>
+      <c r="E45" s="27" t="inlineStr">
+        <is>
+          <t>20231110290</t>
+        </is>
+      </c>
+      <c r="F45" s="22"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="19">
+        <v>1</v>
+      </c>
+      <c r="L45" s="22"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="22"/>
+      <c r="O45" s="19"/>
+      <c r="P45" s="22"/>
+      <c r="Q45" s="19"/>
+      <c r="R45" s="22"/>
+      <c r="S45" s="19"/>
+      <c r="T45" s="22"/>
+      <c r="U45" s="19"/>
+      <c r="V45" s="22"/>
+      <c r="W45" s="19"/>
+      <c r="X45" s="22"/>
+      <c r="Y45" s="19"/>
+      <c r="Z45" s="22"/>
+      <c r="AA45" s="19"/>
+      <c r="AB45" s="22"/>
       <c r="AC45" s="19"/>
-    </row>
-    <row r="46" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD45" s="19"/>
+    </row>
+    <row r="46" spans="1:30" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="19">
         <v>40</v>
       </c>
@@ -6209,35 +6410,40 @@
       <c r="D46" s="21">
         <v>30906842</v>
       </c>
-      <c r="E46" s="22"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="19"/>
-      <c r="K46" s="22"/>
-      <c r="L46" s="19"/>
-      <c r="M46" s="22"/>
-      <c r="N46" s="19"/>
+      <c r="E46" s="27" t="inlineStr">
+        <is>
+          <t>20241110056</t>
+        </is>
+      </c>
+      <c r="F46" s="22"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="19"/>
+      <c r="N46" s="22"/>
       <c r="O46" s="19"/>
       <c r="P46" s="19"/>
-      <c r="Q46" s="22"/>
-      <c r="R46" s="19"/>
-      <c r="S46" s="22">
+      <c r="Q46" s="19"/>
+      <c r="R46" s="22"/>
+      <c r="S46" s="19"/>
+      <c r="T46" s="22">
         <v>3</v>
       </c>
-      <c r="T46" s="19"/>
-      <c r="U46" s="22"/>
-      <c r="V46" s="19"/>
-      <c r="W46" s="22"/>
-      <c r="X46" s="19"/>
-      <c r="Y46" s="22"/>
-      <c r="Z46" s="19"/>
-      <c r="AA46" s="22"/>
-      <c r="AB46" s="19"/>
+      <c r="U46" s="19"/>
+      <c r="V46" s="22"/>
+      <c r="W46" s="19"/>
+      <c r="X46" s="22"/>
+      <c r="Y46" s="19"/>
+      <c r="Z46" s="22"/>
+      <c r="AA46" s="19"/>
+      <c r="AB46" s="22"/>
       <c r="AC46" s="19"/>
-    </row>
-    <row r="47" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD46" s="19"/>
+    </row>
+    <row r="47" spans="1:30" ht="14" x14ac:dyDescent="0.15">
       <c r="A47" s="19">
         <v>41</v>
       </c>
@@ -6250,33 +6456,38 @@
       <c r="D47" s="21">
         <v>27545301</v>
       </c>
-      <c r="E47" s="22"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="22"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="22"/>
-      <c r="N47" s="19"/>
-      <c r="O47" s="22"/>
-      <c r="P47" s="19"/>
-      <c r="Q47" s="22"/>
-      <c r="R47" s="19"/>
-      <c r="S47" s="22"/>
-      <c r="T47" s="19"/>
-      <c r="U47" s="22"/>
-      <c r="V47" s="19"/>
-      <c r="W47" s="22"/>
-      <c r="X47" s="19"/>
-      <c r="Y47" s="22"/>
-      <c r="Z47" s="19"/>
-      <c r="AA47" s="22"/>
-      <c r="AB47" s="19"/>
+      <c r="E47" s="21" t="inlineStr">
+        <is>
+          <t>20231120067</t>
+        </is>
+      </c>
+      <c r="F47" s="22"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="19"/>
+      <c r="N47" s="22"/>
+      <c r="O47" s="19"/>
+      <c r="P47" s="22"/>
+      <c r="Q47" s="19"/>
+      <c r="R47" s="22"/>
+      <c r="S47" s="19"/>
+      <c r="T47" s="22"/>
+      <c r="U47" s="19"/>
+      <c r="V47" s="22"/>
+      <c r="W47" s="19"/>
+      <c r="X47" s="22"/>
+      <c r="Y47" s="19"/>
+      <c r="Z47" s="22"/>
+      <c r="AA47" s="19"/>
+      <c r="AB47" s="22"/>
       <c r="AC47" s="19"/>
-    </row>
-    <row r="48" spans="1:29" ht="14" x14ac:dyDescent="0.15">
+      <c r="AD47" s="19"/>
+    </row>
+    <row r="48" spans="1:30" ht="14" x14ac:dyDescent="0.15">
       <c r="A48" s="19"/>
       <c r="B48" s="22"/>
       <c r="C48" s="19"/>
@@ -6306,8 +6517,9 @@
       <c r="AA48" s="19"/>
       <c r="AB48" s="19"/>
       <c r="AC48" s="19"/>
-    </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD48" s="19"/>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A49" s="19"/>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
@@ -6337,8 +6549,9 @@
       <c r="AA49" s="19"/>
       <c r="AB49" s="19"/>
       <c r="AC49" s="19"/>
-    </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD49" s="19"/>
+    </row>
+    <row r="50" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A50" s="19"/>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
@@ -6368,8 +6581,9 @@
       <c r="AA50" s="19"/>
       <c r="AB50" s="19"/>
       <c r="AC50" s="19"/>
-    </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD50" s="19"/>
+    </row>
+    <row r="51" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A51" s="19"/>
       <c r="B51" s="19"/>
       <c r="C51" s="19"/>
@@ -6399,8 +6613,9 @@
       <c r="AA51" s="19"/>
       <c r="AB51" s="19"/>
       <c r="AC51" s="19"/>
-    </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD51" s="19"/>
+    </row>
+    <row r="52" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A52" s="19"/>
       <c r="B52" s="19"/>
       <c r="C52" s="19"/>
@@ -6430,8 +6645,9 @@
       <c r="AA52" s="19"/>
       <c r="AB52" s="19"/>
       <c r="AC52" s="19"/>
-    </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD52" s="19"/>
+    </row>
+    <row r="53" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A53" s="19"/>
       <c r="B53" s="19"/>
       <c r="C53" s="19"/>
@@ -6461,8 +6677,9 @@
       <c r="AA53" s="19"/>
       <c r="AB53" s="19"/>
       <c r="AC53" s="19"/>
-    </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD53" s="19"/>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A54" s="19"/>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
@@ -6492,8 +6709,9 @@
       <c r="AA54" s="19"/>
       <c r="AB54" s="19"/>
       <c r="AC54" s="19"/>
-    </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD54" s="19"/>
+    </row>
+    <row r="55" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A55" s="19"/>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -6523,8 +6741,9 @@
       <c r="AA55" s="19"/>
       <c r="AB55" s="19"/>
       <c r="AC55" s="19"/>
-    </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD55" s="19"/>
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A56" s="19"/>
       <c r="B56" s="19"/>
       <c r="C56" s="19"/>
@@ -6554,8 +6773,9 @@
       <c r="AA56" s="19"/>
       <c r="AB56" s="19"/>
       <c r="AC56" s="19"/>
-    </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD56" s="19"/>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A57" s="19"/>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
@@ -6585,8 +6805,9 @@
       <c r="AA57" s="19"/>
       <c r="AB57" s="19"/>
       <c r="AC57" s="19"/>
-    </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD57" s="19"/>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A58" s="19"/>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
@@ -6616,8 +6837,9 @@
       <c r="AA58" s="19"/>
       <c r="AB58" s="19"/>
       <c r="AC58" s="19"/>
-    </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD58" s="19"/>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A59" s="19"/>
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
@@ -6647,8 +6869,9 @@
       <c r="AA59" s="19"/>
       <c r="AB59" s="19"/>
       <c r="AC59" s="19"/>
-    </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD59" s="19"/>
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A60" s="19"/>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
@@ -6678,8 +6901,9 @@
       <c r="AA60" s="19"/>
       <c r="AB60" s="19"/>
       <c r="AC60" s="19"/>
-    </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.15">
+      <c r="AD60" s="19"/>
+    </row>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A61" s="19"/>
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
@@ -6709,25 +6933,27 @@
       <c r="AA61" s="19"/>
       <c r="AB61" s="19"/>
       <c r="AC61" s="19"/>
+      <c r="AD61" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Datos Tesis Upstream/Computacion Emergente/2526-2/Emergente 2526-2.xlsx
+++ b/Datos Tesis Upstream/Computacion Emergente/2526-2/Emergente 2526-2.xlsx
@@ -15,6 +15,7 @@
   <sheets>
     <sheet name="COMPURACION EMERGENTE" sheetId="1" r:id="rId1"/>
     <sheet name="Estandar" sheetId="2" r:id="rId2"/>
+    <sheet name="Cronograma" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5390,25 +5391,23 @@
         <v>18</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C24" s="19" t="s">
         <v>112</v>
       </c>
       <c r="D24" s="21">
-        <v>25736710</v>
+        <v>29506315</v>
       </c>
       <c r="E24" s="27" t="inlineStr">
         <is>
-          <t>20161110446</t>
+          <t>20211110506</t>
         </is>
       </c>
       <c r="F24" s="22"/>
       <c r="G24" s="19"/>
       <c r="H24" s="22"/>
-      <c r="I24" s="19">
-        <v>1</v>
-      </c>
+      <c r="I24" s="19"/>
       <c r="J24" s="22"/>
       <c r="K24" s="19"/>
       <c r="L24" s="22"/>
@@ -5436,23 +5435,25 @@
         <v>19</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>112</v>
       </c>
       <c r="D25" s="21">
-        <v>29506315</v>
+        <v>25736710</v>
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>20211110506</t>
+          <t>20161110446</t>
         </is>
       </c>
       <c r="F25" s="22"/>
       <c r="G25" s="19"/>
       <c r="H25" s="22"/>
-      <c r="I25" s="19"/>
+      <c r="I25" s="19">
+        <v>1</v>
+      </c>
       <c r="J25" s="22"/>
       <c r="K25" s="19"/>
       <c r="L25" s="22"/>
@@ -6958,4 +6959,365 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semana</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dia_sesion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">administrativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sin_clase</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">administrativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema = código del catálogo de la asignatura. Si la sesión no cubre contenido nuevo: tema = 0 y tipo_sesion indica la causa (evaluacion, repaso, sin_clase, administrativa). Si tema &gt; 0 la sesión es de contenido y tipo_sesion queda vacío.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Datos Tesis Upstream/Computacion Emergente/2526-2/Emergente 2526-2.xlsx
+++ b/Datos Tesis Upstream/Computacion Emergente/2526-2/Emergente 2526-2.xlsx
@@ -7049,7 +7049,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -7060,7 +7060,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -7071,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7082,7 +7082,7 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -7125,7 +7125,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -7168,7 +7168,7 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -7179,7 +7179,7 @@
         <v>1</v>
       </c>
       <c r="C16">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -7222,7 +7222,7 @@
         <v>2</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -7233,7 +7233,7 @@
         <v>1</v>
       </c>
       <c r="C20">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -7244,7 +7244,7 @@
         <v>2</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -7271,7 +7271,7 @@
         <v>2</v>
       </c>
       <c r="C23">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
